--- a/outputs/templates/收益法测算_模板.xlsx
+++ b/outputs/templates/收益法测算_模板.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>B6*(1-B7)</f>
+        <f>ROUND(B6*(1-B7),0)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>SUM(B10:B16)</f>
+        <f>ROUND(SUM(B10:B16),0)</f>
         <v/>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>B8+B9-B17</f>
+        <f>ROUND(B8+B9-B17,0)</f>
         <v/>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -966,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="15">
-        <f>IF(A6&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A6&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C6" s="16">
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>B6*C6</f>
+        <f>ROUND(B6*C6,0)</f>
         <v/>
       </c>
     </row>
@@ -983,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="15">
-        <f>IF(A7&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A7&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C7" s="16">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>B7*C7</f>
+        <f>ROUND(B7*C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="15">
-        <f>IF(A8&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A8&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C8" s="16">
@@ -1008,7 +1008,7 @@
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>B8*C8</f>
+        <f>ROUND(B8*C8,0)</f>
         <v/>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="15">
-        <f>IF(A9&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A9&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C9" s="16">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>B9*C9</f>
+        <f>ROUND(B9*C9,0)</f>
         <v/>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="15">
-        <f>IF(A10&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A10&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C10" s="16">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>B10*C10</f>
+        <f>ROUND(B10*C10,0)</f>
         <v/>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="15">
-        <f>IF(A11&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A11&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C11" s="16">
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>B11*C11</f>
+        <f>ROUND(B11*C11,0)</f>
         <v/>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="15">
-        <f>IF(A12&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A12&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C12" s="16">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>B12*C12</f>
+        <f>ROUND(B12*C12,0)</f>
         <v/>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="15">
-        <f>IF(A13&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A13&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C13" s="16">
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>B13*C13</f>
+        <f>ROUND(B13*C13,0)</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="15">
-        <f>IF(A14&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A14&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C14" s="16">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>B14*C14</f>
+        <f>ROUND(B14*C14,0)</f>
         <v/>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="15">
-        <f>IF(A15&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A15&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C15" s="16">
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>B15*C15</f>
+        <f>ROUND(B15*C15,0)</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="15">
-        <f>IF(A16&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A16&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C16" s="16">
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>B16*C16</f>
+        <f>ROUND(B16*C16,0)</f>
         <v/>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="15">
-        <f>IF(A17&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A17&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C17" s="16">
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>B17*C17</f>
+        <f>ROUND(B17*C17,0)</f>
         <v/>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="15">
-        <f>IF(A18&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A18&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C18" s="16">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>B18*C18</f>
+        <f>ROUND(B18*C18,0)</f>
         <v/>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="15">
-        <f>IF(A19&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A19&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C19" s="16">
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>B19*C19</f>
+        <f>ROUND(B19*C19,0)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="15">
-        <f>IF(A20&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A20&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C20" s="16">
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>B20*C20</f>
+        <f>ROUND(B20*C20,0)</f>
         <v/>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="15">
-        <f>IF(A21&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A21&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C21" s="16">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="D21" s="15">
-        <f>B21*C21</f>
+        <f>ROUND(B21*C21,0)</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="15">
-        <f>IF(A22&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A22&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C22" s="16">
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>B22*C22</f>
+        <f>ROUND(B22*C22,0)</f>
         <v/>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="15">
-        <f>IF(A23&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A23&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C23" s="16">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>B23*C23</f>
+        <f>ROUND(B23*C23,0)</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="15">
-        <f>IF(A24&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A24&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C24" s="16">
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D24" s="15">
-        <f>B24*C24</f>
+        <f>ROUND(B24*C24,0)</f>
         <v/>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="15">
-        <f>IF(A25&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A25&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C25" s="16">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="D25" s="15">
-        <f>B25*C25</f>
+        <f>ROUND(B25*C25,0)</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="15">
-        <f>IF(A26&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A26&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C26" s="16">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="D26" s="15">
-        <f>B26*C26</f>
+        <f>ROUND(B26*C26,0)</f>
         <v/>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="15">
-        <f>IF(A27&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A27&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C27" s="16">
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="D27" s="15">
-        <f>B27*C27</f>
+        <f>ROUND(B27*C27,0)</f>
         <v/>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="15">
-        <f>IF(A28&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A28&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C28" s="16">
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="D28" s="15">
-        <f>B28*C28</f>
+        <f>ROUND(B28*C28,0)</f>
         <v/>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="15">
-        <f>IF(A29&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A29&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C29" s="16">
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="D29" s="15">
-        <f>B29*C29</f>
+        <f>ROUND(B29*C29,0)</f>
         <v/>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="15">
-        <f>IF(A30&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A30&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C30" s="16">
@@ -1382,7 +1382,7 @@
         <v/>
       </c>
       <c r="D30" s="15">
-        <f>B30*C30</f>
+        <f>ROUND(B30*C30,0)</f>
         <v/>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="15">
-        <f>IF(A31&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A31&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C31" s="16">
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="D31" s="15">
-        <f>B31*C31</f>
+        <f>ROUND(B31*C31,0)</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="15">
-        <f>IF(A32&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A32&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C32" s="16">
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="D32" s="15">
-        <f>B32*C32</f>
+        <f>ROUND(B32*C32,0)</f>
         <v/>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="15">
-        <f>IF(A33&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A33&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C33" s="16">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="D33" s="15">
-        <f>B33*C33</f>
+        <f>ROUND(B33*C33,0)</f>
         <v/>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="15">
-        <f>IF(A34&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A34&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C34" s="16">
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="D34" s="15">
-        <f>B34*C34</f>
+        <f>ROUND(B34*C34,0)</f>
         <v/>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="15">
-        <f>IF(A35&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A35&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C35" s="16">
@@ -1467,7 +1467,7 @@
         <v/>
       </c>
       <c r="D35" s="15">
-        <f>B35*C35</f>
+        <f>ROUND(B35*C35,0)</f>
         <v/>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="15">
-        <f>IF(A36&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A36&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C36" s="16">
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="D36" s="15">
-        <f>B36*C36</f>
+        <f>ROUND(B36*C36,0)</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="15">
-        <f>IF(A37&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A37&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C37" s="16">
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="D37" s="15">
-        <f>B37*C37</f>
+        <f>ROUND(B37*C37,0)</f>
         <v/>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="15">
-        <f>IF(A38&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A38&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C38" s="16">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="D38" s="15">
-        <f>B38*C38</f>
+        <f>ROUND(B38*C38,0)</f>
         <v/>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="15">
-        <f>IF(A39&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A39&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C39" s="16">
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="D39" s="15">
-        <f>B39*C39</f>
+        <f>ROUND(B39*C39,0)</f>
         <v/>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="15">
-        <f>IF(A40&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A40&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C40" s="16">
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="D40" s="15">
-        <f>B40*C40</f>
+        <f>ROUND(B40*C40,0)</f>
         <v/>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="15">
-        <f>IF(A41&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A41&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C41" s="16">
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="D41" s="15">
-        <f>B41*C41</f>
+        <f>ROUND(B41*C41,0)</f>
         <v/>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="15">
-        <f>IF(A42&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A42&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C42" s="16">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="D42" s="15">
-        <f>B42*C42</f>
+        <f>ROUND(B42*C42,0)</f>
         <v/>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="15">
-        <f>IF(A43&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A43&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C43" s="16">
@@ -1603,7 +1603,7 @@
         <v/>
       </c>
       <c r="D43" s="15">
-        <f>B43*C43</f>
+        <f>ROUND(B43*C43,0)</f>
         <v/>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="15">
-        <f>IF(A44&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A44&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C44" s="16">
@@ -1620,7 +1620,7 @@
         <v/>
       </c>
       <c r="D44" s="15">
-        <f>B44*C44</f>
+        <f>ROUND(B44*C44,0)</f>
         <v/>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="15">
-        <f>IF(A45&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A45&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C45" s="16">
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="D45" s="15">
-        <f>B45*C45</f>
+        <f>ROUND(B45*C45,0)</f>
         <v/>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="15">
-        <f>IF(A46&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A46&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C46" s="16">
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>B46*C46</f>
+        <f>ROUND(B46*C46,0)</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="15">
-        <f>IF(A47&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A47&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C47" s="16">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>B47*C47</f>
+        <f>ROUND(B47*C47,0)</f>
         <v/>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="15">
-        <f>IF(A48&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A48&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C48" s="16">
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>B48*C48</f>
+        <f>ROUND(B48*C48,0)</f>
         <v/>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="15">
-        <f>IF(A49&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A49&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C49" s="16">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>B49*C49</f>
+        <f>ROUND(B49*C49,0)</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
         <v>45</v>
       </c>
       <c r="B50" s="15">
-        <f>IF(A50&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A50&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C50" s="16">
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>B50*C50</f>
+        <f>ROUND(B50*C50,0)</f>
         <v/>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="15">
-        <f>IF(A51&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A51&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C51" s="16">
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="D51" s="15">
-        <f>B51*C51</f>
+        <f>ROUND(B51*C51,0)</f>
         <v/>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="15">
-        <f>IF(A52&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A52&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C52" s="16">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="D52" s="15">
-        <f>B52*C52</f>
+        <f>ROUND(B52*C52,0)</f>
         <v/>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="15">
-        <f>IF(A53&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A53&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C53" s="16">
@@ -1773,7 +1773,7 @@
         <v/>
       </c>
       <c r="D53" s="15">
-        <f>B53*C53</f>
+        <f>ROUND(B53*C53,0)</f>
         <v/>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="15">
-        <f>IF(A54&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A54&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C54" s="16">
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="D54" s="15">
-        <f>B54*C54</f>
+        <f>ROUND(B54*C54,0)</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="15">
-        <f>IF(A55&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A55&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C55" s="16">
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="D55" s="15">
-        <f>B55*C55</f>
+        <f>ROUND(B55*C55,0)</f>
         <v/>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="15">
-        <f>IF(A56&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A56&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C56" s="16">
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
       <c r="D56" s="15">
-        <f>B56*C56</f>
+        <f>ROUND(B56*C56,0)</f>
         <v/>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="15">
-        <f>IF(A57&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A57&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C57" s="16">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="D57" s="15">
-        <f>B57*C57</f>
+        <f>ROUND(B57*C57,0)</f>
         <v/>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="15">
-        <f>IF(A58&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A58&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C58" s="16">
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="D58" s="15">
-        <f>B58*C58</f>
+        <f>ROUND(B58*C58,0)</f>
         <v/>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="15">
-        <f>IF(A59&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A59&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C59" s="16">
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="D59" s="15">
-        <f>B59*C59</f>
+        <f>ROUND(B59*C59,0)</f>
         <v/>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="15">
-        <f>IF(A60&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A60&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C60" s="16">
@@ -1892,7 +1892,7 @@
         <v/>
       </c>
       <c r="D60" s="15">
-        <f>B60*C60</f>
+        <f>ROUND(B60*C60,0)</f>
         <v/>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="15">
-        <f>IF(A61&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A61&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C61" s="16">
@@ -1909,7 +1909,7 @@
         <v/>
       </c>
       <c r="D61" s="15">
-        <f>B61*C61</f>
+        <f>ROUND(B61*C61,0)</f>
         <v/>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="15">
-        <f>IF(A62&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A62&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C62" s="16">
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="D62" s="15">
-        <f>B62*C62</f>
+        <f>ROUND(B62*C62,0)</f>
         <v/>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="15">
-        <f>IF(A63&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A63&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C63" s="16">
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="D63" s="15">
-        <f>B63*C63</f>
+        <f>ROUND(B63*C63,0)</f>
         <v/>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="15">
-        <f>IF(A64&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A64&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C64" s="16">
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="D64" s="15">
-        <f>B64*C64</f>
+        <f>ROUND(B64*C64,0)</f>
         <v/>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="15">
-        <f>IF(A65&lt;=$C$3, 净收益测算!B18, 0)</f>
+        <f>ROUND(IF(A65&lt;=$C$3, 净收益测算!B18, 0),0)</f>
         <v/>
       </c>
       <c r="C65" s="16">
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="D65" s="15">
-        <f>B65*C65</f>
+        <f>ROUND(B65*C65,0)</f>
         <v/>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D66" s="18">
-        <f>SUM(D6:D65)</f>
+        <f>ROUND(SUM(D6:D65),0)</f>
         <v/>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D70" s="22">
-        <f>IF(C68*C69=0,0,C68/(1+C69)^C3)</f>
+        <f>ROUND(IF(C68*C69=0,0,C68/(1+C69)^C3),0)</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="D72" s="18">
-        <f>D66+D70</f>
+        <f>ROUND(D66+D70,0)</f>
         <v/>
       </c>
     </row>

--- a/outputs/templates/收益法测算_模板.xlsx
+++ b/outputs/templates/收益法测算_模板.xlsx
@@ -645,10 +645,8 @@
           <t>潜在毛租金收入 (元/m²·年)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>如: 600</t>
-        </is>
+      <c r="B6" s="6" t="n">
+        <v>600</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -662,7 +660,9 @@
           <t>空置和收租损失率</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
+      <c r="B7" s="8" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>4.3.8条; 区域空置率调查</t>
@@ -691,10 +691,8 @@
           <t>其他收入 (元/m²·年)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>如: 50</t>
-        </is>
+      <c r="B9" s="6" t="n">
+        <v>50</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>

--- a/outputs/templates/收益法测算_模板.xlsx
+++ b/outputs/templates/收益法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="净收益测算" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收益价值" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="净收益测算" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="收益价值" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/templates/收益法测算_模板.xlsx
+++ b/outputs/templates/收益法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="净收益测算" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="收益价值" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="净收益测算" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收益价值" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
